--- a/ig/ch-elm/CodeSystem-ch-elm-results-component-vs.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-results-component-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/CodeSystem-ch-elm-results-component-vs.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-results-component-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/CodeSystem-ch-elm-results-component-vs.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-results-component-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -142,9 +142,6 @@
   </si>
   <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-component-gene-tb</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-component-antibiotic-cpe</t>
   </si>
   <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-component-antibiotic-tb</t>
@@ -457,7 +454,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -504,16 +501,6 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/ch-elm/CodeSystem-ch-elm-results-component-vs.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-results-component-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
